--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/104.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/104.xlsx
@@ -426,13 +426,13 @@
         <v>-8.348492466598284</v>
       </c>
       <c r="E2">
-        <v>-9.132562022554389</v>
+        <v>-11.94739806708618</v>
       </c>
       <c r="F2">
-        <v>-3.285599337178341</v>
+        <v>-3.741240341986</v>
       </c>
       <c r="G2">
-        <v>-8.481089134994832</v>
+        <v>-9.947164227061077</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.616432165109417</v>
       </c>
       <c r="E3">
-        <v>-10.2914981475454</v>
+        <v>-11.78993396889146</v>
       </c>
       <c r="F3">
-        <v>-2.872676410965649</v>
+        <v>-3.916214731744534</v>
       </c>
       <c r="G3">
-        <v>-7.80246371544517</v>
+        <v>-9.628580498180392</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.816035656530312</v>
       </c>
       <c r="E4">
-        <v>-9.805493260094204</v>
+        <v>-13.70678267465023</v>
       </c>
       <c r="F4">
-        <v>-3.424582820020042</v>
+        <v>-4.062219456692364</v>
       </c>
       <c r="G4">
-        <v>-7.860053965646332</v>
+        <v>-9.235724680126159</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.040590352894986</v>
       </c>
       <c r="E5">
-        <v>-10.86828082495436</v>
+        <v>-13.8763196845494</v>
       </c>
       <c r="F5">
-        <v>-3.202192680125264</v>
+        <v>-3.653073885836438</v>
       </c>
       <c r="G5">
-        <v>-7.090186600488817</v>
+        <v>-8.039720582608119</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.287963229357096</v>
       </c>
       <c r="E6">
-        <v>-11.83300881365242</v>
+        <v>-14.16632768847461</v>
       </c>
       <c r="F6">
-        <v>-3.084364044016257</v>
+        <v>-3.926546958359653</v>
       </c>
       <c r="G6">
-        <v>-6.780922057301182</v>
+        <v>-8.588890429390119</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.574396022482182</v>
       </c>
       <c r="E7">
-        <v>-12.89274871550542</v>
+        <v>-15.47459477234256</v>
       </c>
       <c r="F7">
-        <v>-3.124397383858752</v>
+        <v>-3.977557823024046</v>
       </c>
       <c r="G7">
-        <v>-6.606191463738448</v>
+        <v>-8.24439175002802</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.904186906405656</v>
       </c>
       <c r="E8">
-        <v>-13.19975208238142</v>
+        <v>-16.39915066811858</v>
       </c>
       <c r="F8">
-        <v>-2.93539542050121</v>
+        <v>-3.882098420260237</v>
       </c>
       <c r="G8">
-        <v>-5.762631354876757</v>
+        <v>-7.871203883022598</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.283816221418147</v>
       </c>
       <c r="E9">
-        <v>-13.83481169179509</v>
+        <v>-16.53441165825369</v>
       </c>
       <c r="F9">
-        <v>-3.474838213613082</v>
+        <v>-3.862198550142784</v>
       </c>
       <c r="G9">
-        <v>-5.46536422872344</v>
+        <v>-7.007297161276545</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.706339764519395</v>
       </c>
       <c r="E10">
-        <v>-15.42801488869967</v>
+        <v>-17.04652772683311</v>
       </c>
       <c r="F10">
-        <v>-3.227602850206139</v>
+        <v>-4.057529240457713</v>
       </c>
       <c r="G10">
-        <v>-5.612157128480264</v>
+        <v>-6.385586640638034</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.182727025935058</v>
       </c>
       <c r="E11">
-        <v>-15.35149726339206</v>
+        <v>-17.8890593729082</v>
       </c>
       <c r="F11">
-        <v>-2.86344177115924</v>
+        <v>-3.974163173407374</v>
       </c>
       <c r="G11">
-        <v>-4.818235339434405</v>
+        <v>-5.915502416243683</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.715546232320366</v>
       </c>
       <c r="E12">
-        <v>-15.86145777834383</v>
+        <v>-18.54394464152745</v>
       </c>
       <c r="F12">
-        <v>-2.593175308852262</v>
+        <v>-3.747723973647712</v>
       </c>
       <c r="G12">
-        <v>-4.766276327195544</v>
+        <v>-5.844679915522054</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.306359933987069</v>
       </c>
       <c r="E13">
-        <v>-17.20074038069032</v>
+        <v>-19.00656901767704</v>
       </c>
       <c r="F13">
-        <v>-2.413070011400788</v>
+        <v>-3.547679044443451</v>
       </c>
       <c r="G13">
-        <v>-4.11636989019906</v>
+        <v>-5.75448741285015</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.9687683946009322</v>
       </c>
       <c r="E14">
-        <v>-17.37001021062303</v>
+        <v>-19.98093359906343</v>
       </c>
       <c r="F14">
-        <v>-3.077201979451652</v>
+        <v>-3.459842278520203</v>
       </c>
       <c r="G14">
-        <v>-3.907547298672912</v>
+        <v>-4.741006933094287</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.705836638396744</v>
       </c>
       <c r="E15">
-        <v>-19.1551437213947</v>
+        <v>-21.73708940466001</v>
       </c>
       <c r="F15">
-        <v>-2.605971100123306</v>
+        <v>-3.473475549235477</v>
       </c>
       <c r="G15">
-        <v>-3.128893745654171</v>
+        <v>-4.44455751168917</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.5164150744648559</v>
       </c>
       <c r="E16">
-        <v>-19.14488672776733</v>
+        <v>-22.03102359554988</v>
       </c>
       <c r="F16">
-        <v>-2.395757961049681</v>
+        <v>-3.191111609378015</v>
       </c>
       <c r="G16">
-        <v>-3.247014010495368</v>
+        <v>-4.967663433440489</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.4018710551272281</v>
       </c>
       <c r="E17">
-        <v>-20.17099365316535</v>
+        <v>-22.91405791314957</v>
       </c>
       <c r="F17">
-        <v>-2.433873630354695</v>
+        <v>-3.024642067744024</v>
       </c>
       <c r="G17">
-        <v>-2.052701601747894</v>
+        <v>-4.069995768284949</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.3518940686420439</v>
       </c>
       <c r="E18">
-        <v>-21.10072106625813</v>
+        <v>-23.59590571601049</v>
       </c>
       <c r="F18">
-        <v>-1.483397417075917</v>
+        <v>-2.630690411790246</v>
       </c>
       <c r="G18">
-        <v>-2.039525630501595</v>
+        <v>-4.332982195379113</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3524873973157833</v>
       </c>
       <c r="E19">
-        <v>-20.4103642607368</v>
+        <v>-25.2864258193399</v>
       </c>
       <c r="F19">
-        <v>-1.104198156198596</v>
+        <v>-2.184419070675652</v>
       </c>
       <c r="G19">
-        <v>-1.734945509252028</v>
+        <v>-3.789556145107748</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.3905281333515029</v>
       </c>
       <c r="E20">
-        <v>-21.80690035996226</v>
+        <v>-25.16495856103216</v>
       </c>
       <c r="F20">
-        <v>-0.4290215655662053</v>
+        <v>-1.817829218403744</v>
       </c>
       <c r="G20">
-        <v>-2.241607951309787</v>
+        <v>-3.962959209909233</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.4485394030421471</v>
       </c>
       <c r="E21">
-        <v>-23.80259885514259</v>
+        <v>-25.6716540462244</v>
       </c>
       <c r="F21">
-        <v>-0.6448518639982137</v>
+        <v>-1.506688623340431</v>
       </c>
       <c r="G21">
-        <v>-2.342847744446239</v>
+        <v>-3.802076628337271</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5123660499084124</v>
       </c>
       <c r="E22">
-        <v>-24.50493347441421</v>
+        <v>-26.63530425810864</v>
       </c>
       <c r="F22">
-        <v>-0.7145175625736521</v>
+        <v>-1.389692496471237</v>
       </c>
       <c r="G22">
-        <v>-2.145350529209938</v>
+        <v>-4.155858077391486</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.5735529518318815</v>
       </c>
       <c r="E23">
-        <v>-24.99646762862877</v>
+        <v>-26.89581378234789</v>
       </c>
       <c r="F23">
-        <v>0.501331946763767</v>
+        <v>-1.15677463525428</v>
       </c>
       <c r="G23">
-        <v>-2.301909538307611</v>
+        <v>-4.194694087112677</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6267381267181475</v>
       </c>
       <c r="E24">
-        <v>-26.01412895000249</v>
+        <v>-27.36944687881014</v>
       </c>
       <c r="F24">
-        <v>-0.1912329040207876</v>
+        <v>-1.087718615087302</v>
       </c>
       <c r="G24">
-        <v>-2.450010103552447</v>
+        <v>-3.266132410984659</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6709052330706198</v>
       </c>
       <c r="E25">
-        <v>-24.75863670221993</v>
+        <v>-27.68529435542312</v>
       </c>
       <c r="F25">
-        <v>-0.05797758176944515</v>
+        <v>-1.063275149765494</v>
       </c>
       <c r="G25">
-        <v>-2.398521188780162</v>
+        <v>-3.502363009030433</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.7078455994380882</v>
       </c>
       <c r="E26">
-        <v>-26.63454800294936</v>
+        <v>-27.66019755247261</v>
       </c>
       <c r="F26">
-        <v>0.2897735390279957</v>
+        <v>-0.7651829980310783</v>
       </c>
       <c r="G26">
-        <v>-1.448315165916389</v>
+        <v>-4.09365954779966</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.7384356147114072</v>
       </c>
       <c r="E27">
-        <v>-25.50461222550347</v>
+        <v>-28.34889240803313</v>
       </c>
       <c r="F27">
-        <v>0.1060747837831773</v>
+        <v>-0.6475481998943261</v>
       </c>
       <c r="G27">
-        <v>-1.554186412262282</v>
+        <v>-4.356818123261865</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.7635271006373392</v>
       </c>
       <c r="E28">
-        <v>-25.77383000525947</v>
+        <v>-27.71347052069885</v>
       </c>
       <c r="F28">
-        <v>0.4394843797359503</v>
+        <v>-0.375555419919914</v>
       </c>
       <c r="G28">
-        <v>-2.686724041246955</v>
+        <v>-4.166273053658034</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7829091216786617</v>
       </c>
       <c r="E29">
-        <v>-24.8077978160472</v>
+        <v>-27.91347510372162</v>
       </c>
       <c r="F29">
-        <v>0.6531874306775696</v>
+        <v>-0.6723992219783113</v>
       </c>
       <c r="G29">
-        <v>-2.488190625256862</v>
+        <v>-4.494553370423243</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7944186771464598</v>
       </c>
       <c r="E30">
-        <v>-24.18646401135078</v>
+        <v>-27.53302894538922</v>
       </c>
       <c r="F30">
-        <v>0.08090069841210036</v>
+        <v>-0.5914337636612848</v>
       </c>
       <c r="G30">
-        <v>-1.938951257018536</v>
+        <v>-4.208528856921292</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7962816731834256</v>
       </c>
       <c r="E31">
-        <v>-25.15068933943399</v>
+        <v>-27.41296551402385</v>
       </c>
       <c r="F31">
-        <v>0.003655438101046466</v>
+        <v>-0.7853769385765246</v>
       </c>
       <c r="G31">
-        <v>-2.526894213156481</v>
+        <v>-4.430282439323832</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7861810422172585</v>
       </c>
       <c r="E32">
-        <v>-25.14473892458791</v>
+        <v>-27.28740451521318</v>
       </c>
       <c r="F32">
-        <v>-0.1178345819283346</v>
+        <v>-0.6608376981374385</v>
       </c>
       <c r="G32">
-        <v>-2.425369713103652</v>
+        <v>-4.226346213013649</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7615431833012705</v>
       </c>
       <c r="E33">
-        <v>-24.64719095689117</v>
+        <v>-27.06770107025704</v>
       </c>
       <c r="F33">
-        <v>0.06046073274802256</v>
+        <v>-0.7592063272198798</v>
       </c>
       <c r="G33">
-        <v>-2.854624979362172</v>
+        <v>-4.511566263949558</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7210466143183859</v>
       </c>
       <c r="E34">
-        <v>-24.24875769980029</v>
+        <v>-26.10532788804296</v>
       </c>
       <c r="F34">
-        <v>-0.02266096591849103</v>
+        <v>-1.220300474640169</v>
       </c>
       <c r="G34">
-        <v>-3.010376215348263</v>
+        <v>-4.33331324993304</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.6643043464105779</v>
       </c>
       <c r="E35">
-        <v>-22.72601302998106</v>
+        <v>-25.97224509390555</v>
       </c>
       <c r="F35">
-        <v>-0.1481586274426161</v>
+        <v>-1.146688433757793</v>
       </c>
       <c r="G35">
-        <v>-2.619152496244891</v>
+        <v>-4.343460072010906</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5922277649175228</v>
       </c>
       <c r="E36">
-        <v>-23.05741581481039</v>
+        <v>-25.54039622711208</v>
       </c>
       <c r="F36">
-        <v>-0.3390641790917902</v>
+        <v>-1.045821448588509</v>
       </c>
       <c r="G36">
-        <v>-3.394690825911177</v>
+        <v>-4.516594982623711</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5074029720973268</v>
       </c>
       <c r="E37">
-        <v>-23.20654299235699</v>
+        <v>-24.97451358663958</v>
       </c>
       <c r="F37">
-        <v>-0.2437754200129575</v>
+        <v>-1.185541350051299</v>
       </c>
       <c r="G37">
-        <v>-1.926884318527893</v>
+        <v>-4.517227296821711</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.4127040435823424</v>
       </c>
       <c r="E38">
-        <v>-21.89050957556588</v>
+        <v>-24.20154835827033</v>
       </c>
       <c r="F38">
-        <v>-0.6307257146782738</v>
+        <v>-1.239837519835195</v>
       </c>
       <c r="G38">
-        <v>-2.537319121059646</v>
+        <v>-4.287938912771789</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.3114201314835132</v>
       </c>
       <c r="E39">
-        <v>-21.11452838350752</v>
+        <v>-24.0434819730326</v>
       </c>
       <c r="F39">
-        <v>-0.3918088167302431</v>
+        <v>-1.443842045224838</v>
       </c>
       <c r="G39">
-        <v>-2.763316822843533</v>
+        <v>-4.404367488842418</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2082014777433733</v>
       </c>
       <c r="E40">
-        <v>-20.50563429691017</v>
+        <v>-23.72353622744267</v>
       </c>
       <c r="F40">
-        <v>-0.5864884102665717</v>
+        <v>-1.526249691190138</v>
       </c>
       <c r="G40">
-        <v>-1.133551806588024</v>
+        <v>-3.851681842697711</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1074384427404971</v>
       </c>
       <c r="E41">
-        <v>-20.68594001799957</v>
+        <v>-23.21141563038924</v>
       </c>
       <c r="F41">
-        <v>-0.5439293782129415</v>
+        <v>-1.520953938384041</v>
       </c>
       <c r="G41">
-        <v>-2.144138869542564</v>
+        <v>-3.257683898768438</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.01349684628116844</v>
       </c>
       <c r="E42">
-        <v>-19.84322270449017</v>
+        <v>-22.18798956160375</v>
       </c>
       <c r="F42">
-        <v>-0.5590802180101445</v>
+        <v>-1.608657337155438</v>
       </c>
       <c r="G42">
-        <v>-2.172086494985092</v>
+        <v>-3.830236128694312</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.06745929915168408</v>
       </c>
       <c r="E43">
-        <v>-18.37313060195812</v>
+        <v>-21.03935571498019</v>
       </c>
       <c r="F43">
-        <v>-0.5142531160076492</v>
+        <v>-1.85274076259473</v>
       </c>
       <c r="G43">
-        <v>-2.186715795723131</v>
+        <v>-3.670638038791587</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.1303777224408586</v>
       </c>
       <c r="E44">
-        <v>-19.32990659029872</v>
+        <v>-20.96738014910228</v>
       </c>
       <c r="F44">
-        <v>-0.8849011401858712</v>
+        <v>-1.752615994618353</v>
       </c>
       <c r="G44">
-        <v>-2.826472100096209</v>
+        <v>-3.085548772908494</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1710141704404882</v>
       </c>
       <c r="E45">
-        <v>-18.94108728352613</v>
+        <v>-20.17508739366829</v>
       </c>
       <c r="F45">
-        <v>-0.7485734032375454</v>
+        <v>-1.772312086354717</v>
       </c>
       <c r="G45">
-        <v>-2.077017558733841</v>
+        <v>-3.819453681872905</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.1827123533862486</v>
       </c>
       <c r="E46">
-        <v>-18.42607299158179</v>
+        <v>-19.70675714026903</v>
       </c>
       <c r="F46">
-        <v>-0.7050045913199026</v>
+        <v>-1.86890883756257</v>
       </c>
       <c r="G46">
-        <v>-2.566577722535725</v>
+        <v>-3.396501694321158</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.1599600972025493</v>
       </c>
       <c r="E47">
-        <v>-17.08278721821253</v>
+        <v>-19.56329961218004</v>
       </c>
       <c r="F47">
-        <v>-0.8012501147489688</v>
+        <v>-1.913677125479467</v>
       </c>
       <c r="G47">
-        <v>-2.53684571304753</v>
+        <v>-3.620549484782414</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.09921304496323555</v>
       </c>
       <c r="E48">
-        <v>-16.27101296759754</v>
+        <v>-18.14142670088166</v>
       </c>
       <c r="F48">
-        <v>-0.6099229240917697</v>
+        <v>-1.749089634584636</v>
       </c>
       <c r="G48">
-        <v>-2.493384871207978</v>
+        <v>-2.931293903506153</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.003958932941749584</v>
       </c>
       <c r="E49">
-        <v>-15.56930780621299</v>
+        <v>-18.65155476937172</v>
       </c>
       <c r="F49">
-        <v>-0.9759900765325105</v>
+        <v>-1.599544467357241</v>
       </c>
       <c r="G49">
-        <v>-2.257677339357409</v>
+        <v>-3.328910286045858</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.1504214991881697</v>
       </c>
       <c r="E50">
-        <v>-14.57706480944432</v>
+        <v>-17.86499053355743</v>
       </c>
       <c r="F50">
-        <v>-0.8643849647207359</v>
+        <v>-1.886177812808732</v>
       </c>
       <c r="G50">
-        <v>-2.165250218446497</v>
+        <v>-3.115446309673652</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3372108252168146</v>
       </c>
       <c r="E51">
-        <v>-14.55382468083696</v>
+        <v>-16.98979047599101</v>
       </c>
       <c r="F51">
-        <v>-1.033443982855879</v>
+        <v>-1.798901023249776</v>
       </c>
       <c r="G51">
-        <v>-2.30514063075394</v>
+        <v>-3.940828212979205</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.5627808289520174</v>
       </c>
       <c r="E52">
-        <v>-13.59486143955066</v>
+        <v>-16.42991259205269</v>
       </c>
       <c r="F52">
-        <v>-0.8351162592776209</v>
+        <v>-2.068489881021264</v>
       </c>
       <c r="G52">
-        <v>-2.813272955031135</v>
+        <v>-3.944360565069608</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8220125065961933</v>
       </c>
       <c r="E53">
-        <v>-12.97489070553055</v>
+        <v>-16.62628081044729</v>
       </c>
       <c r="F53">
-        <v>-0.9972145061270394</v>
+        <v>-2.093756743541454</v>
       </c>
       <c r="G53">
-        <v>-1.940305270144098</v>
+        <v>-4.588029934270105</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.108240355935753</v>
       </c>
       <c r="E54">
-        <v>-12.28646302993649</v>
+        <v>-15.87322728228977</v>
       </c>
       <c r="F54">
-        <v>-1.267172815760176</v>
+        <v>-2.058539531778836</v>
       </c>
       <c r="G54">
-        <v>-2.176890096562574</v>
+        <v>-3.782557651837728</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.419072864473497</v>
       </c>
       <c r="E55">
-        <v>-11.28753147705849</v>
+        <v>-15.54738546354186</v>
       </c>
       <c r="F55">
-        <v>-0.9240837467056906</v>
+        <v>-2.097423097666245</v>
       </c>
       <c r="G55">
-        <v>-2.759357410378565</v>
+        <v>-4.600619938955953</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.748654307371691</v>
       </c>
       <c r="E56">
-        <v>-12.29180662926554</v>
+        <v>-14.86536105019464</v>
       </c>
       <c r="F56">
-        <v>-0.7642129798024001</v>
+        <v>-1.980680451222308</v>
       </c>
       <c r="G56">
-        <v>-3.116740732979507</v>
+        <v>-4.53394886234057</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.090974108149259</v>
       </c>
       <c r="E57">
-        <v>-11.65455070995815</v>
+        <v>-14.28574354805688</v>
       </c>
       <c r="F57">
-        <v>-1.447537392208726</v>
+        <v>-2.09997529763427</v>
       </c>
       <c r="G57">
-        <v>-2.822701388726979</v>
+        <v>-4.760996007060406</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.443410772401613</v>
       </c>
       <c r="E58">
-        <v>-11.15421773074668</v>
+        <v>-13.3218895548423</v>
       </c>
       <c r="F58">
-        <v>-1.044240923583967</v>
+        <v>-2.015230827225672</v>
       </c>
       <c r="G58">
-        <v>-3.897827536969612</v>
+        <v>-4.479497009310638</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.798561870081428</v>
       </c>
       <c r="E59">
-        <v>-11.32118256740949</v>
+        <v>-13.90965831019386</v>
       </c>
       <c r="F59">
-        <v>-1.194511740656214</v>
+        <v>-2.091251760515389</v>
       </c>
       <c r="G59">
-        <v>-3.765627521949896</v>
+        <v>-4.810816406880898</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.150047192710316</v>
       </c>
       <c r="E60">
-        <v>-10.07150035177877</v>
+        <v>-12.96072111036055</v>
       </c>
       <c r="F60">
-        <v>-0.7375378926974504</v>
+        <v>-2.340992106948397</v>
       </c>
       <c r="G60">
-        <v>-3.622135236095725</v>
+        <v>-5.343483184149632</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.493060128030781</v>
       </c>
       <c r="E61">
-        <v>-10.73030727888866</v>
+        <v>-12.80044482980707</v>
       </c>
       <c r="F61">
-        <v>-0.9116159889261553</v>
+        <v>-2.12296663489897</v>
       </c>
       <c r="G61">
-        <v>-4.113430125760187</v>
+        <v>-5.187516762703488</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.816313293822857</v>
       </c>
       <c r="E62">
-        <v>-7.281810923411575</v>
+        <v>-12.47780917065659</v>
       </c>
       <c r="F62">
-        <v>-1.191473289022746</v>
+        <v>-2.069650423752586</v>
       </c>
       <c r="G62">
-        <v>-3.605377254575934</v>
+        <v>-5.141188988426928</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.112867045286844</v>
       </c>
       <c r="E63">
-        <v>-9.665477372251043</v>
+        <v>-11.730620016339</v>
       </c>
       <c r="F63">
-        <v>-1.510140430307896</v>
+        <v>-1.988056234576834</v>
       </c>
       <c r="G63">
-        <v>-4.440071722483458</v>
+        <v>-5.252271033451633</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.378418139586359</v>
       </c>
       <c r="E64">
-        <v>-9.187655437331706</v>
+        <v>-11.89837280747914</v>
       </c>
       <c r="F64">
-        <v>-1.32511960068821</v>
+        <v>-1.904217169739497</v>
       </c>
       <c r="G64">
-        <v>-4.119607603736467</v>
+        <v>-5.970272081645385</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.60438164215148</v>
       </c>
       <c r="E65">
-        <v>-7.805854992527204</v>
+        <v>-11.4523135892496</v>
       </c>
       <c r="F65">
-        <v>-1.267852905397874</v>
+        <v>-2.088516491351344</v>
       </c>
       <c r="G65">
-        <v>-5.707130058910876</v>
+        <v>-6.356056574427735</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.790886214733899</v>
       </c>
       <c r="E66">
-        <v>-8.128169130023142</v>
+        <v>-11.25463211339276</v>
       </c>
       <c r="F66">
-        <v>-1.44737586056518</v>
+        <v>-2.38235331973758</v>
       </c>
       <c r="G66">
-        <v>-4.79363798607762</v>
+        <v>-5.785252312546597</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.938119990959469</v>
       </c>
       <c r="E67">
-        <v>-8.184639200898792</v>
+        <v>-11.36778509342242</v>
       </c>
       <c r="F67">
-        <v>-1.518088615537757</v>
+        <v>-2.168741389210268</v>
       </c>
       <c r="G67">
-        <v>-5.448016970097659</v>
+        <v>-6.062566780734727</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.042465065014188</v>
       </c>
       <c r="E68">
-        <v>-7.892656782306229</v>
+        <v>-11.54985239090081</v>
       </c>
       <c r="F68">
-        <v>-1.172767096332727</v>
+        <v>-2.116145029336916</v>
       </c>
       <c r="G68">
-        <v>-5.61553719547586</v>
+        <v>-5.999600204577789</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.110277363301101</v>
       </c>
       <c r="E69">
-        <v>-7.725605904637278</v>
+        <v>-10.56360962219231</v>
       </c>
       <c r="F69">
-        <v>-1.389678414225389</v>
+        <v>-2.161357322181714</v>
       </c>
       <c r="G69">
-        <v>-5.663033592327784</v>
+        <v>-5.639733972822393</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.143988177367836</v>
       </c>
       <c r="E70">
-        <v>-8.50442644989845</v>
+        <v>-10.65333227770628</v>
       </c>
       <c r="F70">
-        <v>-1.939064101273063</v>
+        <v>-2.457081999878929</v>
       </c>
       <c r="G70">
-        <v>-5.330922974373637</v>
+        <v>-5.48548903505667</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.142456157158083</v>
       </c>
       <c r="E71">
-        <v>-8.812163429563695</v>
+        <v>-10.92535318287303</v>
       </c>
       <c r="F71">
-        <v>-1.554853217608805</v>
+        <v>-2.323308948000836</v>
       </c>
       <c r="G71">
-        <v>-5.297327558241113</v>
+        <v>-6.248391012399558</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.111091246734466</v>
       </c>
       <c r="E72">
-        <v>-7.999687265477519</v>
+        <v>-10.6303819714354</v>
       </c>
       <c r="F72">
-        <v>-1.670718622973177</v>
+        <v>-2.322671105100681</v>
       </c>
       <c r="G72">
-        <v>-4.295010238043672</v>
+        <v>-6.81654352730374</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.04926397664442</v>
       </c>
       <c r="E73">
-        <v>-8.102578723405797</v>
+        <v>-11.82724406624066</v>
       </c>
       <c r="F73">
-        <v>-1.702812889627241</v>
+        <v>-2.771467310059008</v>
       </c>
       <c r="G73">
-        <v>-4.53417728998278</v>
+        <v>-6.070488916210203</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.955820460636787</v>
       </c>
       <c r="E74">
-        <v>-8.045719203765488</v>
+        <v>-11.16601440553666</v>
       </c>
       <c r="F74">
-        <v>-1.691943880935109</v>
+        <v>-2.4948596952836</v>
       </c>
       <c r="G74">
-        <v>-5.248245410075879</v>
+        <v>-6.271710495178184</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.833998364768484</v>
       </c>
       <c r="E75">
-        <v>-8.649822164862721</v>
+        <v>-11.85930113374096</v>
       </c>
       <c r="F75">
-        <v>-1.51815157146037</v>
+        <v>-2.497649636696229</v>
       </c>
       <c r="G75">
-        <v>-4.063626278667392</v>
+        <v>-6.344353795946412</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.680231979094565</v>
       </c>
       <c r="E76">
-        <v>-8.540178752189007</v>
+        <v>-12.49430187299252</v>
       </c>
       <c r="F76">
-        <v>-1.689853909977846</v>
+        <v>-2.098581155295359</v>
       </c>
       <c r="G76">
-        <v>-3.362664608364267</v>
+        <v>-6.023833397925254</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.494534496667576</v>
       </c>
       <c r="E77">
-        <v>-9.213893415732148</v>
+        <v>-12.43177270389461</v>
       </c>
       <c r="F77">
-        <v>-1.678395932062323</v>
+        <v>-2.476044986463815</v>
       </c>
       <c r="G77">
-        <v>-4.258855770209292</v>
+        <v>-5.692672906540879</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.281416842989177</v>
       </c>
       <c r="E78">
-        <v>-9.6031066997434</v>
+        <v>-13.42279301268121</v>
       </c>
       <c r="F78">
-        <v>-2.06318335943893</v>
+        <v>-2.489114138977782</v>
       </c>
       <c r="G78">
-        <v>-3.710497007084412</v>
+        <v>-5.568332126631392</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.042436912660348</v>
       </c>
       <c r="E79">
-        <v>-10.16990409196545</v>
+        <v>-14.2456076829269</v>
       </c>
       <c r="F79">
-        <v>-2.003468838473322</v>
+        <v>-2.716721336775392</v>
       </c>
       <c r="G79">
-        <v>-3.218950515958966</v>
+        <v>-5.625912445195936</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.785780991819117</v>
       </c>
       <c r="E80">
-        <v>-11.4374375521344</v>
+        <v>-14.40597906143454</v>
       </c>
       <c r="F80">
-        <v>-2.002739875158858</v>
+        <v>-2.714619768674489</v>
       </c>
       <c r="G80">
-        <v>-3.723672978330712</v>
+        <v>-5.063523590075625</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.519268510381044</v>
       </c>
       <c r="E81">
-        <v>-11.83799919200887</v>
+        <v>-14.45182533228819</v>
       </c>
       <c r="F81">
-        <v>-2.178248561892198</v>
+        <v>-2.80635731669752</v>
       </c>
       <c r="G81">
-        <v>-2.925156152076344</v>
+        <v>-5.356443969935879</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.244640262225638</v>
       </c>
       <c r="E82">
-        <v>-12.70647899414791</v>
+        <v>-14.71984306643216</v>
       </c>
       <c r="F82">
-        <v>-1.761348643778666</v>
+        <v>-2.751386027480343</v>
       </c>
       <c r="G82">
-        <v>-2.943172140901058</v>
+        <v>-5.323792059282047</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.970398079623874</v>
       </c>
       <c r="E83">
-        <v>-13.54152960116233</v>
+        <v>-16.56475696257909</v>
       </c>
       <c r="F83">
-        <v>-2.020324458385486</v>
+        <v>-2.777251799632757</v>
       </c>
       <c r="G83">
-        <v>-2.370259061511404</v>
+        <v>-5.100088565556876</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.705126559603225</v>
       </c>
       <c r="E84">
-        <v>-14.24192150508465</v>
+        <v>-17.0220784956657</v>
       </c>
       <c r="F84">
-        <v>-2.172588327428869</v>
+        <v>-2.688680271823225</v>
       </c>
       <c r="G84">
-        <v>-1.739643173372254</v>
+        <v>-4.115601843633949</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.453300246043999</v>
       </c>
       <c r="E85">
-        <v>-15.55151090336284</v>
+        <v>-17.85580678826987</v>
       </c>
       <c r="F85">
-        <v>-2.25412038904941</v>
+        <v>-2.800427862828282</v>
       </c>
       <c r="G85">
-        <v>-2.844166966003614</v>
+        <v>-4.015269139975257</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.226903175265869</v>
       </c>
       <c r="E86">
-        <v>-16.44021939889414</v>
+        <v>-18.95920117955681</v>
       </c>
       <c r="F86">
-        <v>-1.873592426857999</v>
+        <v>-2.917979824224754</v>
       </c>
       <c r="G86">
-        <v>-2.592009333368406</v>
+        <v>-3.79885546752756</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.036104674967355</v>
       </c>
       <c r="E87">
-        <v>-18.49700700843794</v>
+        <v>-20.20551873899983</v>
       </c>
       <c r="F87">
-        <v>-2.004643463450492</v>
+        <v>-2.832088893330682</v>
       </c>
       <c r="G87">
-        <v>-1.759724942613473</v>
+        <v>-3.937838790357243</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.886495848293438</v>
       </c>
       <c r="E88">
-        <v>-19.19039789154441</v>
+        <v>-21.72889739518014</v>
       </c>
       <c r="F88">
-        <v>-2.153789357589737</v>
+        <v>-2.515082628688144</v>
       </c>
       <c r="G88">
-        <v>-2.398617194600801</v>
+        <v>-4.20235800003609</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.793361023471047</v>
       </c>
       <c r="E89">
-        <v>-21.57552250901435</v>
+        <v>-24.0757201794932</v>
       </c>
       <c r="F89">
-        <v>-2.316353975286932</v>
+        <v>-3.099196790730785</v>
       </c>
       <c r="G89">
-        <v>-1.285926286124059</v>
+        <v>-3.47893758879455</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.767262311472811</v>
       </c>
       <c r="E90">
-        <v>-22.91843241904098</v>
+        <v>-24.53889250099773</v>
       </c>
       <c r="F90">
-        <v>-2.231828193872673</v>
+        <v>-2.740935344326624</v>
       </c>
       <c r="G90">
-        <v>-2.247732460557438</v>
+        <v>-3.853019303095576</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.810706488110407</v>
       </c>
       <c r="E91">
-        <v>-24.08510317763709</v>
+        <v>-26.62628353788536</v>
       </c>
       <c r="F91">
-        <v>-2.67708229981663</v>
+        <v>-2.842596733835193</v>
       </c>
       <c r="G91">
-        <v>-1.348810098642515</v>
+        <v>-3.708050513930891</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.932043406013614</v>
       </c>
       <c r="E92">
-        <v>-25.81890190705781</v>
+        <v>-28.05835004417501</v>
       </c>
       <c r="F92">
-        <v>-1.945774705603142</v>
+        <v>-2.967356320003424</v>
       </c>
       <c r="G92">
-        <v>-2.23000779974018</v>
+        <v>-4.485992299658688</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.130133355114008</v>
       </c>
       <c r="E93">
-        <v>-27.92463779215052</v>
+        <v>-29.65381747808342</v>
       </c>
       <c r="F93">
-        <v>-2.154398207630795</v>
+        <v>-2.670775110411714</v>
       </c>
       <c r="G93">
-        <v>-2.3729141190339</v>
+        <v>-4.239611568989508</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.393220574300379</v>
       </c>
       <c r="E94">
-        <v>-30.39410523801332</v>
+        <v>-31.8610840146651</v>
       </c>
       <c r="F94">
-        <v>-2.468141533073705</v>
+        <v>-2.859594832940639</v>
       </c>
       <c r="G94">
-        <v>-1.966101040986099</v>
+        <v>-4.055353225364753</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.713880220572794</v>
       </c>
       <c r="E95">
-        <v>-30.30952240049806</v>
+        <v>-33.53268641782747</v>
       </c>
       <c r="F95">
-        <v>-2.652710902458865</v>
+        <v>-2.854818466496097</v>
       </c>
       <c r="G95">
-        <v>-2.384120315684333</v>
+        <v>-4.659008030632078</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.077149925846354</v>
       </c>
       <c r="E96">
-        <v>-33.85949053730202</v>
+        <v>-36.00123911194072</v>
       </c>
       <c r="F96">
-        <v>-2.840959051479859</v>
+        <v>-3.200143299170738</v>
       </c>
       <c r="G96">
-        <v>-2.807810554891338</v>
+        <v>-4.233298358646119</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.457595468775203</v>
       </c>
       <c r="E97">
-        <v>-35.75582525580604</v>
+        <v>-39.25598017852562</v>
       </c>
       <c r="F97">
-        <v>-2.981050061539102</v>
+        <v>-3.083723716013893</v>
       </c>
       <c r="G97">
-        <v>-2.841468871389108</v>
+        <v>-4.80481107727266</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.843016027825162</v>
       </c>
       <c r="E98">
-        <v>-39.25373405541782</v>
+        <v>-40.02179721067377</v>
       </c>
       <c r="F98">
-        <v>-3.178662075681341</v>
+        <v>-2.939002960540403</v>
       </c>
       <c r="G98">
-        <v>-3.383709746357414</v>
+        <v>-4.814656639706453</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.206025579961326</v>
       </c>
       <c r="E99">
-        <v>-41.77051499771276</v>
+        <v>-42.19489188239357</v>
       </c>
       <c r="F99">
-        <v>-3.302231297891749</v>
+        <v>-3.192511550288746</v>
       </c>
       <c r="G99">
-        <v>-2.556490490277566</v>
+        <v>-4.803519964512344</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.538907905724853</v>
       </c>
       <c r="E100">
-        <v>-43.3819385097872</v>
+        <v>-45.14913926348849</v>
       </c>
       <c r="F100">
-        <v>-3.092654344983474</v>
+        <v>-3.476025264101294</v>
       </c>
       <c r="G100">
-        <v>-3.383828925996828</v>
+        <v>-5.69861533578387</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.817356674408615</v>
       </c>
       <c r="E101">
-        <v>-45.96187807906711</v>
+        <v>-47.4798746438893</v>
       </c>
       <c r="F101">
-        <v>-3.553632520967371</v>
+        <v>-3.897522621300364</v>
       </c>
       <c r="G101">
-        <v>-3.966935175101898</v>
+        <v>-5.584007559759841</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.06406230605703</v>
       </c>
       <c r="E102">
-        <v>-48.70585482656388</v>
+        <v>-49.20487681255013</v>
       </c>
       <c r="F102">
-        <v>-3.7801802368568</v>
+        <v>-3.565368001962832</v>
       </c>
       <c r="G102">
-        <v>-3.680692165594354</v>
+        <v>-6.073941815207663</v>
       </c>
     </row>
   </sheetData>
